--- a/artfynd/A 50438-2022 artfynd.xlsx
+++ b/artfynd/A 50438-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50438-2022 artfynd.xlsx
+++ b/artfynd/A 50438-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109947090</v>
+        <v>109947005</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörbäcken, Hjd</t>
+          <t>Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461358.2721358464</v>
+        <v>461420</v>
       </c>
       <c r="R2" t="n">
-        <v>6873543.730751621</v>
+        <v>6873366</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109947076</v>
+        <v>109946982</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,14 +805,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörbäcken, Hjd</t>
+          <t>Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461350.7151709556</v>
+        <v>461373</v>
       </c>
       <c r="R3" t="n">
-        <v>6873582.824126637</v>
+        <v>6873389</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,22 +839,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,12 +874,7 @@
         <v>109946986</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461380.0250913156</v>
+        <v>461380</v>
       </c>
       <c r="R4" t="n">
-        <v>6873386.979247333</v>
+        <v>6873387</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2023-05-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +969,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109947061</v>
+        <v>109947002</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,14 +1001,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sörbäcken, Hjd</t>
+          <t>Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461298.1681108015</v>
+        <v>461415</v>
       </c>
       <c r="R5" t="n">
-        <v>6873638.877571302</v>
+        <v>6873365</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1038,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,37 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109947005</v>
+        <v>109947027</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461419.334175811</v>
+        <v>461439</v>
       </c>
       <c r="R6" t="n">
-        <v>6873366.79316581</v>
+        <v>6873260</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1136,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109947107</v>
+        <v>109947032</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461378.8747696364</v>
+        <v>461443</v>
       </c>
       <c r="R7" t="n">
-        <v>6873410.021929822</v>
+        <v>6873243</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,19 +1234,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109946982</v>
+        <v>109947036</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,10 +1299,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461372.9869739867</v>
+        <v>461455</v>
       </c>
       <c r="R8" t="n">
-        <v>6873388.939176172</v>
+        <v>6873239</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1424,22 +1329,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,15 +1361,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109947032</v>
+        <v>109947061</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,14 +1393,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Hjd</t>
+          <t>Sörbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461442.8762114102</v>
+        <v>461298</v>
       </c>
       <c r="R9" t="n">
-        <v>6873242.914828777</v>
+        <v>6873639</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1540,19 +1430,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,12 +1462,7 @@
         <v>109947066</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461294.3016870569</v>
+        <v>461294</v>
       </c>
       <c r="R10" t="n">
-        <v>6873629.992351053</v>
+        <v>6873630</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,19 +1528,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,15 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109947002</v>
+        <v>109947070</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,14 +1589,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Hjd</t>
+          <t>Sörbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461415.5531017393</v>
+        <v>461307</v>
       </c>
       <c r="R11" t="n">
-        <v>6873365.426084222</v>
+        <v>6873629</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1766,19 +1626,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,12 +1658,7 @@
         <v>109947074</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461326.2542394962</v>
+        <v>461327</v>
       </c>
       <c r="R12" t="n">
-        <v>6873625.399061177</v>
+        <v>6873625</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,19 +1724,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,15 +1753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109947027</v>
+        <v>109947076</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,14 +1785,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Hjd</t>
+          <t>Sörbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461438.8322233208</v>
+        <v>461351</v>
       </c>
       <c r="R13" t="n">
-        <v>6873259.88112966</v>
+        <v>6873582</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,19 +1822,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,15 +1851,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109947102</v>
+        <v>109947086</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461345.6676240692</v>
+        <v>461347</v>
       </c>
       <c r="R14" t="n">
-        <v>6873511.445801632</v>
+        <v>6873556</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2105,24 +1920,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Större bestånd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,15 +1949,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109947070</v>
+        <v>109947090</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2190,10 +1985,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461307.4677338462</v>
+        <v>461359</v>
       </c>
       <c r="R15" t="n">
-        <v>6873628.902554494</v>
+        <v>6873544</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2223,19 +2018,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,15 +2047,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109947086</v>
+        <v>109947102</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461347.1110658626</v>
+        <v>461346</v>
       </c>
       <c r="R16" t="n">
-        <v>6873555.606914987</v>
+        <v>6873512</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2336,19 +2116,14 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Större bestånd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2372,6 +2147,104 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>109947107</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>461379</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6873410</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50438-2022 artfynd.xlsx
+++ b/artfynd/A 50438-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947005</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109946982</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109946986</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947002</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947027</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947032</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947036</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947061</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947066</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947070</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947074</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947076</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947086</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947090</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947102</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2245,8 +2325,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109947107</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>